--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +755,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +890,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,14 +915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,6 +880,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,9 +910,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,37 +2087,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,10 +2194,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,50 +2205,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R14" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,12 +2276,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R5" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,9 +1161,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,37 +1202,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R6" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,19 +1294,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B13" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,50 +2087,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R13" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2171,12 +2158,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2194,10 +2197,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,37 +2208,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R14" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,28 +2292,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B2" t="n">
-        <v>91806</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +755,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244108</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>446594</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,13 +902,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -912,12 +922,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244213</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,29 +956,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>447044</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,23 +1025,19 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1045,14 +1050,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,37 +1081,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R5" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,7 +1165,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,19 +1173,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,50 +1204,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R6" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,6 +1275,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,9 +1284,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>91806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,29 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +891,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -922,12 +912,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244213</v>
+        <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>91806</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,28 +946,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -987,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447044</v>
+        <v>446594</v>
       </c>
       <c r="R4" t="n">
-        <v>7000989</v>
+        <v>7000953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,19 +1016,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1050,9 +1045,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,37 +2087,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,10 +2194,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,50 +2205,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R14" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,12 +2276,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R5" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,9 +1161,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,37 +1202,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R6" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,19 +1294,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244108</v>
       </c>
       <c r="B2" t="n">
-        <v>91810</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446594</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +756,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>91812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +890,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,14 +915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,29 +946,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +1026,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,37 +1081,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R5" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,7 +1165,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,19 +1173,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,50 +1204,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R6" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,6 +1275,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,9 +1284,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57718</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244108</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131244111</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131244211</v>
+        <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,50 +1081,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446698</v>
+        <v>447044</v>
       </c>
       <c r="R5" t="n">
-        <v>7000864</v>
+        <v>7000989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,6 +1152,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,9 +1161,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244216</v>
+        <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>58046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,37 +1202,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447044</v>
+        <v>446698</v>
       </c>
       <c r="R6" t="n">
-        <v>7000989</v>
+        <v>7000864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1286,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1284,19 +1294,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57718</v>
+        <v>57719</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244108</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>91813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446594</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000953</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,23 +755,19 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>91813</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,6 +880,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,9 +910,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244111</v>
+        <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,28 +946,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -977,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446673</v>
+        <v>446594</v>
       </c>
       <c r="R4" t="n">
-        <v>7000892</v>
+        <v>7000953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,13 +1027,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B13" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,50 +2087,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R13" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2171,12 +2158,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2194,10 +2197,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,37 +2208,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R14" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,28 +2292,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244213</v>
+        <v>131244111</v>
       </c>
       <c r="B2" t="n">
-        <v>91813</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447044</v>
+        <v>446673</v>
       </c>
       <c r="R2" t="n">
-        <v>7000989</v>
+        <v>7000892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +755,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,9 +785,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>91814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R3" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +890,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,14 +915,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,7 +938,7 @@
         <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244217</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57719</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131244111</v>
+        <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,28 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446673</v>
+        <v>447044</v>
       </c>
       <c r="R2" t="n">
-        <v>7000892</v>
+        <v>7000989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244213</v>
+        <v>131244108</v>
       </c>
       <c r="B3" t="n">
-        <v>91814</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +811,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -852,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447044</v>
+        <v>446594</v>
       </c>
       <c r="R3" t="n">
-        <v>7000989</v>
+        <v>7000953</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +881,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -915,9 +910,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,29 +946,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -978,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +1026,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131244108</v>
+        <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,29 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446594</v>
+        <v>446673</v>
       </c>
       <c r="R3" t="n">
-        <v>7000953</v>
+        <v>7000892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +891,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244111</v>
+        <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,28 +946,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -977,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446673</v>
+        <v>446594</v>
       </c>
       <c r="R4" t="n">
-        <v>7000892</v>
+        <v>7000953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Vissa bålar är fertila med apothecier.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,13 +1027,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>58050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,37 +2087,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446792</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,10 +2194,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131244189</v>
+        <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>58047</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,50 +2205,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446792</v>
+        <v>447029</v>
       </c>
       <c r="R14" t="n">
-        <v>7001280</v>
+        <v>7000963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,12 +2276,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57992</v>
+        <v>57995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131244108</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>131244211</v>
       </c>
       <c r="B6" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131244110</v>
       </c>
       <c r="B8" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131244112</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131244109</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>131244210</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131244214</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>131244189</v>
       </c>
       <c r="B13" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131244217</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>131244190</v>
       </c>
       <c r="B15" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>131244215</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>131244212</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131244213</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,11 +803,11 @@
         <v>131244111</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -935,42 +935,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131244108</v>
+        <v>131244112</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -978,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446594</v>
+        <v>446676</v>
       </c>
       <c r="R4" t="n">
-        <v>7000953</v>
+        <v>7000910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +1022,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1047,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1073,11 +1069,11 @@
         <v>131244216</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1191,61 +1187,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131244211</v>
+        <v>131244217</v>
       </c>
       <c r="B6" t="n">
-        <v>58061</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446698</v>
+        <v>447029</v>
       </c>
       <c r="R6" t="n">
-        <v>7000864</v>
+        <v>7000963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,6 +1269,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,9 +1278,19 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,11 +1311,11 @@
         <v>131244218</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1435,32 +1429,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131244110</v>
+        <v>131244108</v>
       </c>
       <c r="B8" t="n">
-        <v>57090</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1468,24 +1462,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446729</v>
+        <v>446594</v>
       </c>
       <c r="R8" t="n">
-        <v>7000918</v>
+        <v>7000953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,7 +1512,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färsk spillning, storlek ca 5 x 1,5 cm, och färska spår efter tjäderns gång i snön. Möjligen spår efter en tjädertupp.</t>
+          <t>Ringhack, färska, några meter upp på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,7 +1526,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1554,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131244112</v>
+        <v>131244109</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,26 +1575,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1592,10 +1607,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446676</v>
+        <v>446506</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1632,7 +1647,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, färska, några meter upp på en gran i en lucka.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,13 +1656,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1662,12 +1676,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1685,10 +1699,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131244109</v>
+        <v>131244210</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446506</v>
+        <v>446608</v>
       </c>
       <c r="R10" t="n">
-        <v>7000894</v>
+        <v>7000962</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1782,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran i en lucka.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,35 +1834,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131244210</v>
+        <v>131227105</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1856,20 +1874,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Värsångsflon, Jmt</t>
+          <t>Hallhögåsarna, Hallhögåsarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446608</v>
+        <v>446758</v>
       </c>
       <c r="R11" t="n">
-        <v>7000962</v>
+        <v>7000931</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1903,7 +1925,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Färska födosökspår i utglesad tallkrona och lega/trampspår kring en tall för födosök.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,27 +1939,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1955,48 +1957,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131244214</v>
+        <v>131244110</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446996</v>
+        <v>446729</v>
       </c>
       <c r="R12" t="n">
-        <v>7001011</v>
+        <v>7000918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2031,34 +2042,23 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning, storlek ca 5 x 1,5 cm, och färska spår efter tjäderns gång i snön. Möjligen spår efter en tjädertupp.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2076,48 +2076,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131244217</v>
+        <v>131244212</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>57807</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102622</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447029</v>
+        <v>446765</v>
       </c>
       <c r="R13" t="n">
-        <v>7000963</v>
+        <v>7001140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,28 +2171,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2200,7 +2197,7 @@
         <v>131244189</v>
       </c>
       <c r="B14" t="n">
-        <v>58061</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2315,37 +2312,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131244190</v>
+        <v>131244211</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2366,10 +2363,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446864</v>
+        <v>446698</v>
       </c>
       <c r="R15" t="n">
-        <v>7001361</v>
+        <v>7000864</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2416,6 +2413,11 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrskog med förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2433,10 +2435,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131244215</v>
+        <v>131244190</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>58057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,37 +2446,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Värsångsflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446792</v>
+        <v>446864</v>
       </c>
       <c r="R16" t="n">
-        <v>7001066</v>
+        <v>7001361</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2515,28 +2530,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2551,124 +2550,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>131244212</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57780</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>102622</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Pärluggla</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Aegolius funereus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Värsångsflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>446765</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7001140</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53500-2024 artfynd.xlsx
+++ b/artfynd/A 53500-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244213</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1063,6 +1078,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244112</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1184,6 +1204,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1305,6 +1330,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244217</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1426,6 +1456,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244218</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1561,6 +1596,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244108</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1696,6 +1736,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244109</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1831,6 +1876,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244210</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1954,6 +2004,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131227105</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2073,6 +2128,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244110</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2191,6 +2251,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244212</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2309,6 +2374,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244189</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2432,6 +2502,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244211</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2550,8 +2625,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131244190</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>